--- a/Deliverables/Core-Production-Files/BOM/John Wollam_LCSC BOM.xlsx
+++ b/Deliverables/Core-Production-Files/BOM/John Wollam_LCSC BOM.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="276">
   <si>
     <t>S. No.</t>
   </si>
@@ -768,6 +768,90 @@
   </si>
   <si>
     <t>C386081</t>
+  </si>
+  <si>
+    <t>C60474</t>
+  </si>
+  <si>
+    <t>C77009</t>
+  </si>
+  <si>
+    <t>C327025</t>
+  </si>
+  <si>
+    <t>C161300</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOQ-205 </t>
+  </si>
+  <si>
+    <t>C125094</t>
+  </si>
+  <si>
+    <t>C89458</t>
+  </si>
+  <si>
+    <t>C380163</t>
+  </si>
+  <si>
+    <t>C231329</t>
+  </si>
+  <si>
+    <t>C226259</t>
+  </si>
+  <si>
+    <t>C60490</t>
+  </si>
+  <si>
+    <t>C130276</t>
+  </si>
+  <si>
+    <t>C137632</t>
+  </si>
+  <si>
+    <t>C138006</t>
+  </si>
+  <si>
+    <t>C138030</t>
+  </si>
+  <si>
+    <t>C106232</t>
+  </si>
+  <si>
+    <t>C163475</t>
+  </si>
+  <si>
+    <t>C159873</t>
+  </si>
+  <si>
+    <t>C105871</t>
+  </si>
+  <si>
+    <t>C105875</t>
+  </si>
+  <si>
+    <t>C227137</t>
+  </si>
+  <si>
+    <t>C137902</t>
+  </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
+    <t>C208835</t>
+  </si>
+  <si>
+    <t>RMS04FT2400</t>
+  </si>
+  <si>
+    <t>C131551</t>
+  </si>
+  <si>
+    <t>RK73B1ETTP270J</t>
   </si>
 </sst>
 </file>
@@ -778,9 +862,9 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,12 +944,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
@@ -881,13 +959,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF444444"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -914,12 +992,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -937,7 +1009,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1004,19 +1076,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1050,12 +1109,171 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1072,64 +1290,20 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1137,7 +1311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1167,27 +1341,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1197,38 +1361,24 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1244,13 +1394,10 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1259,48 +1406,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1308,41 +1415,250 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1628,17 +1944,17 @@
   <dimension ref="A1:V61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1646,167 +1962,167 @@
     <col min="16" max="17" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="51" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="43.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="119" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="121"/>
     </row>
     <row r="2" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="26" t="s">
+      <c r="M2" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="P2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="R2" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="S2" s="23" t="s">
+      <c r="S2" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="T2" s="22" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
+      <c r="A3" s="20">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="49" t="s">
         <v>239</v>
       </c>
-      <c r="I3" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="36">
+      <c r="K3" s="51">
         <v>485</v>
       </c>
       <c r="L3" s="2">
         <v>4</v>
       </c>
-      <c r="M3" s="36">
+      <c r="M3" s="51">
         <f>L3*110*1.1</f>
         <v>484.00000000000006</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3" s="53">
         <v>0.13150000000000001</v>
       </c>
-      <c r="P3" s="70">
-        <f>O3*L3</f>
+      <c r="P3" s="54">
+        <f t="shared" ref="P3:P47" si="0">O3*L3</f>
         <v>0.52600000000000002</v>
       </c>
-      <c r="Q3" s="70">
+      <c r="Q3" s="54">
         <f>R3*K3</f>
         <v>46.414499999999997</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="53">
         <v>9.5699999999999993E-2</v>
       </c>
-      <c r="S3" s="70">
-        <f>R3*M3</f>
+      <c r="S3" s="54">
+        <f t="shared" ref="S3:S47" si="1">R3*M3</f>
         <v>46.318800000000003</v>
       </c>
-      <c r="T3" s="36"/>
+      <c r="T3" s="55"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
+      <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="112"/>
+      <c r="C4" s="99" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -1830,47 +2146,47 @@
       <c r="J4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="31" t="s">
         <v>53</v>
       </c>
       <c r="L4" s="6">
         <v>1</v>
       </c>
-      <c r="M4" s="36">
-        <f t="shared" ref="M4:M50" si="0">L4*110*1.1</f>
+      <c r="M4" s="26">
+        <f t="shared" ref="M4:M50" si="2">L4*110*1.1</f>
         <v>121.00000000000001</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="N4" s="43" t="s">
         <v>240</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="28">
         <v>0.67335999999999996</v>
       </c>
-      <c r="P4" s="70">
-        <f>O4*L4</f>
+      <c r="P4" s="42">
+        <f t="shared" si="0"/>
         <v>0.67335999999999996</v>
       </c>
-      <c r="Q4" s="70">
+      <c r="Q4" s="42">
         <f>R4*M4</f>
         <v>63.08456000000001</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="30">
         <v>0.52136000000000005</v>
       </c>
-      <c r="S4" s="70">
-        <f>R4*M4</f>
+      <c r="S4" s="42">
+        <f t="shared" si="1"/>
         <v>63.08456000000001</v>
       </c>
-      <c r="T4" s="36"/>
+      <c r="T4" s="56"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="20">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="112"/>
+      <c r="C5" s="99" t="s">
         <v>68</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -1888,55 +2204,55 @@
       <c r="H5" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="31" t="s">
         <v>241</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="26">
         <v>150</v>
       </c>
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="36">
+      <c r="M5" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N5" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="28">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="P5" s="42">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N5" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="38">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="P5" s="70">
-        <f>O5*L5</f>
-        <v>1.6799999999999999E-2</v>
-      </c>
-      <c r="Q5" s="70">
+      <c r="Q5" s="42">
         <f>R5*K5</f>
         <v>2.52</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="28">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="S5" s="70">
-        <f>R5*M5</f>
+      <c r="S5" s="42">
+        <f t="shared" si="1"/>
         <v>2.0327999999999999</v>
       </c>
-      <c r="T5" s="72" t="s">
+      <c r="T5" s="57" t="s">
         <v>244</v>
       </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="20">
         <v>4</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="112"/>
+      <c r="C6" s="99" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -1954,53 +2270,53 @@
       <c r="H6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="31" t="s">
         <v>53</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="26">
         <v>150</v>
       </c>
       <c r="L6" s="6">
         <v>1</v>
       </c>
-      <c r="M6" s="36">
+      <c r="M6" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="34">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="P6" s="42">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N6" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="53">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="P6" s="70">
-        <f>O6*L6</f>
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="Q6" s="70">
+      <c r="Q6" s="42">
         <f>R6*K6</f>
         <v>1.155</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="34">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="S6" s="70">
-        <f>R6*M6</f>
+      <c r="S6" s="42">
+        <f t="shared" si="1"/>
         <v>0.93170000000000019</v>
       </c>
-      <c r="T6" s="36"/>
+      <c r="T6" s="56"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="112"/>
+      <c r="C7" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -2018,53 +2334,53 @@
       <c r="H7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="31" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="31" t="s">
         <v>53</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
       </c>
-      <c r="M7" s="36">
+      <c r="M7" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="O7" s="28">
+        <v>0.46481</v>
+      </c>
+      <c r="P7" s="42">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N7" s="61" t="s">
-        <v>240</v>
-      </c>
-      <c r="O7" s="38">
-        <v>0.46481</v>
-      </c>
-      <c r="P7" s="70">
-        <f>O7*L7</f>
         <v>0.92962</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="42">
         <f>R7*M7</f>
         <v>72.28540000000001</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="28">
         <v>0.29870000000000002</v>
       </c>
-      <c r="S7" s="70">
-        <f>R7*M7</f>
+      <c r="S7" s="42">
+        <f t="shared" si="1"/>
         <v>72.28540000000001</v>
       </c>
-      <c r="T7" s="54"/>
+      <c r="T7" s="58"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="28" t="s">
+      <c r="B8" s="112"/>
+      <c r="C8" s="99" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -2082,53 +2398,53 @@
       <c r="H8" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="31" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="26">
         <v>240</v>
       </c>
       <c r="L8" s="6">
         <v>2</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="28">
+        <v>0.52</v>
+      </c>
+      <c r="P8" s="29">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N8" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" s="38">
-        <v>0.52</v>
-      </c>
-      <c r="P8" s="39">
-        <f>O8*L8</f>
         <v>1.04</v>
       </c>
-      <c r="Q8" s="70">
+      <c r="Q8" s="42">
         <f>R8*K8</f>
         <v>4.4639999999999995</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="28">
         <v>1.8599999999999998E-2</v>
       </c>
-      <c r="S8" s="39">
-        <f>R8*M8</f>
+      <c r="S8" s="29">
+        <f t="shared" si="1"/>
         <v>4.5011999999999999</v>
       </c>
-      <c r="T8" s="36"/>
+      <c r="T8" s="56"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="20">
         <v>7</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="28" t="s">
+      <c r="B9" s="112"/>
+      <c r="C9" s="99" t="s">
         <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -2137,7 +2453,7 @@
       <c r="E9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="33" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -2152,47 +2468,47 @@
       <c r="J9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="26">
         <v>250</v>
       </c>
       <c r="L9" s="6">
         <v>2</v>
       </c>
-      <c r="M9" s="36">
+      <c r="M9" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="30">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="P9" s="29">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N9" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9" s="40">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="P9" s="39">
-        <f>O9*L9</f>
         <v>3.0599999999999999E-2</v>
       </c>
-      <c r="Q9" s="70">
+      <c r="Q9" s="42">
         <f>R9*K9</f>
         <v>3.8249999999999997</v>
       </c>
-      <c r="R9" s="40">
+      <c r="R9" s="30">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="S9" s="39">
-        <f>R9*M9</f>
+      <c r="S9" s="29">
+        <f t="shared" si="1"/>
         <v>3.7026000000000003</v>
       </c>
-      <c r="T9" s="36"/>
+      <c r="T9" s="56"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="20">
         <v>8</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="112"/>
+      <c r="C10" s="99" t="s">
         <v>83</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -2210,53 +2526,53 @@
       <c r="H10" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="I10" s="73" t="s">
+      <c r="I10" s="44" t="s">
         <v>53</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="26">
         <v>250</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" s="28">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="P10" s="29">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N10" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10" s="38">
-        <v>3.7900000000000003E-2</v>
-      </c>
-      <c r="P10" s="39">
-        <f>O10*L10</f>
         <v>7.5800000000000006E-2</v>
       </c>
-      <c r="Q10" s="39">
+      <c r="Q10" s="29">
         <f>R10*K10</f>
         <v>6.9750000000000005</v>
       </c>
-      <c r="R10" s="40">
+      <c r="R10" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="S10" s="39">
-        <f>R10*M10</f>
+      <c r="S10" s="29">
+        <f t="shared" si="1"/>
         <v>6.7518000000000011</v>
       </c>
-      <c r="T10" s="54"/>
+      <c r="T10" s="58"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="20">
         <v>9</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="112"/>
+      <c r="C11" s="99" t="s">
         <v>86</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -2274,56 +2590,56 @@
       <c r="H11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="73" t="s">
+      <c r="I11" s="44" t="s">
         <v>53</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="41" t="s">
+      <c r="K11" s="31" t="s">
         <v>53</v>
       </c>
       <c r="L11" s="6">
         <v>4</v>
       </c>
-      <c r="M11" s="36">
+      <c r="M11" s="26">
+        <f t="shared" si="2"/>
+        <v>484.00000000000006</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="O11" s="28">
+        <v>0.12515999999999999</v>
+      </c>
+      <c r="P11" s="29">
         <f t="shared" si="0"/>
-        <v>484.00000000000006</v>
-      </c>
-      <c r="N11" s="61" t="s">
-        <v>240</v>
-      </c>
-      <c r="O11" s="38">
-        <v>0.12515999999999999</v>
-      </c>
-      <c r="P11" s="39">
-        <f>O11*L11</f>
         <v>0.50063999999999997</v>
       </c>
-      <c r="Q11" s="70">
+      <c r="Q11" s="42">
         <f>R11*M11</f>
         <v>60.577440000000003</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="28">
         <v>0.12515999999999999</v>
       </c>
-      <c r="S11" s="39">
-        <f>R11*M11</f>
+      <c r="S11" s="29">
+        <f t="shared" si="1"/>
         <v>60.577440000000003</v>
       </c>
-      <c r="T11" s="54"/>
+      <c r="T11" s="58"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" spans="1:22" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="20">
         <v>10</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="55" t="s">
+      <c r="B12" s="112"/>
+      <c r="C12" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="60" t="s">
+      <c r="D12" s="35" t="s">
         <v>90</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -2335,26 +2651,47 @@
       <c r="G12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
+      <c r="H12" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="63">
+      <c r="K12" s="31">
+        <v>1700</v>
+      </c>
+      <c r="L12" s="38">
         <v>14</v>
       </c>
-      <c r="M12" s="36">
+      <c r="M12" s="26">
+        <f t="shared" si="2"/>
+        <v>1694.0000000000002</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="28">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P12" s="29">
         <f t="shared" si="0"/>
-        <v>1694.0000000000002</v>
-      </c>
-      <c r="N12" s="42"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="36"/>
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="Q12" s="29">
+        <f>R12*K12</f>
+        <v>1.7</v>
+      </c>
+      <c r="R12" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="S12" s="29">
+        <f t="shared" si="1"/>
+        <v>1.6940000000000002</v>
+      </c>
+      <c r="T12" s="56"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
     </row>
@@ -2362,8 +2699,8 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="112"/>
+      <c r="C13" s="99" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -2378,26 +2715,47 @@
       <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="41"/>
+      <c r="H13" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="36"/>
+      <c r="K13" s="26">
+        <v>150</v>
+      </c>
       <c r="L13" s="6">
         <v>1</v>
       </c>
-      <c r="M13" s="36">
+      <c r="M13" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="28">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="P13" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N13" s="42"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="56"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="Q13" s="29">
+        <f>R13*K13</f>
+        <v>0.96000000000000008</v>
+      </c>
+      <c r="R13" s="28">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="S13" s="29">
+        <f t="shared" si="1"/>
+        <v>0.77440000000000009</v>
+      </c>
+      <c r="T13" s="59"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
     </row>
@@ -2405,8 +2763,8 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="112"/>
+      <c r="C14" s="99" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -2421,26 +2779,47 @@
       <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="41"/>
+      <c r="H14" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J14" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="K14" s="36"/>
+      <c r="K14" s="26">
+        <v>200</v>
+      </c>
       <c r="L14" s="6">
         <v>1</v>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="P14" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N14" s="42"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="36"/>
+        <v>2E-3</v>
+      </c>
+      <c r="Q14" s="29">
+        <f>R14*K14</f>
+        <v>0.4</v>
+      </c>
+      <c r="R14" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="S14" s="29">
+        <f t="shared" si="1"/>
+        <v>0.24200000000000002</v>
+      </c>
+      <c r="T14" s="56"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
     </row>
@@ -2448,42 +2827,63 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="113"/>
+      <c r="C15" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="5" t="s">
+      <c r="H15" s="62" t="s">
+        <v>251</v>
+      </c>
+      <c r="I15" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="K15" s="36"/>
+      <c r="K15" s="64">
+        <v>240</v>
+      </c>
       <c r="L15" s="10">
         <v>2</v>
       </c>
-      <c r="M15" s="36">
+      <c r="M15" s="64">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N15" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="66">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="P15" s="67">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N15" s="42"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="36"/>
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="Q15" s="67">
+        <f>R15*K15</f>
+        <v>4.0559999999999992</v>
+      </c>
+      <c r="R15" s="66">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="S15" s="67">
+        <f t="shared" si="1"/>
+        <v>4.0898000000000003</v>
+      </c>
+      <c r="T15" s="68"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
     </row>
@@ -2491,42 +2891,67 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="36"/>
+      <c r="H16" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K16" s="69" t="s">
+        <v>53</v>
+      </c>
       <c r="L16" s="2">
         <v>2</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="51">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N16" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="O16" s="53">
+        <v>7.5130000000000002E-2</v>
+      </c>
+      <c r="P16" s="72">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N16" s="42"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="57"/>
+        <v>0.15026</v>
+      </c>
+      <c r="Q16" s="54">
+        <f>R16*M16</f>
+        <v>18.181460000000001</v>
+      </c>
+      <c r="R16" s="53">
+        <v>7.5130000000000002E-2</v>
+      </c>
+      <c r="S16" s="72">
+        <f t="shared" si="1"/>
+        <v>18.181460000000001</v>
+      </c>
+      <c r="T16" s="73" t="s">
+        <v>253</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
     </row>
@@ -2534,40 +2959,63 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="58" t="s">
+      <c r="B17" s="113"/>
+      <c r="C17" s="102" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="60" t="s">
+      <c r="D17" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="36"/>
+      <c r="H17" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" s="64">
+        <v>2660</v>
+      </c>
       <c r="L17" s="10">
         <v>22</v>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="64">
+        <f t="shared" si="2"/>
+        <v>2662</v>
+      </c>
+      <c r="N17" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17" s="66">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="P17" s="67">
         <f t="shared" si="0"/>
-        <v>2662</v>
-      </c>
-      <c r="N17" s="42"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="39"/>
-      <c r="T17" s="54"/>
+        <v>0.54559999999999997</v>
+      </c>
+      <c r="Q17" s="77">
+        <f>R17*K17</f>
+        <v>48.411999999999999</v>
+      </c>
+      <c r="R17" s="66">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="S17" s="67">
+        <f t="shared" si="1"/>
+        <v>48.448399999999999</v>
+      </c>
+      <c r="T17" s="78"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
     </row>
@@ -2575,42 +3023,65 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="43"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="36"/>
+      <c r="H18" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K18" s="69" t="s">
+        <v>53</v>
+      </c>
       <c r="L18" s="2">
         <v>1</v>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="51">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N18" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="O18" s="53">
+        <v>9.4369999999999996E-2</v>
+      </c>
+      <c r="P18" s="72">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N18" s="42"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="56"/>
+        <v>9.4369999999999996E-2</v>
+      </c>
+      <c r="Q18" s="54">
+        <f>R18*M18</f>
+        <v>8.431280000000001</v>
+      </c>
+      <c r="R18" s="53">
+        <v>6.9680000000000006E-2</v>
+      </c>
+      <c r="S18" s="72">
+        <f t="shared" si="1"/>
+        <v>8.431280000000001</v>
+      </c>
+      <c r="T18" s="79"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
     </row>
@@ -2618,11 +3089,11 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="55" t="s">
+      <c r="B19" s="115"/>
+      <c r="C19" s="100" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D19" s="35" t="s">
         <v>124</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -2634,24 +3105,47 @@
       <c r="G19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="36"/>
+      <c r="H19" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="L19" s="6">
         <v>45</v>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="26">
+        <f t="shared" si="2"/>
+        <v>5445</v>
+      </c>
+      <c r="N19" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="O19" s="28">
+        <v>6.862E-2</v>
+      </c>
+      <c r="P19" s="29">
         <f t="shared" si="0"/>
-        <v>5445</v>
-      </c>
-      <c r="N19" s="42"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="39"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="39"/>
-      <c r="T19" s="36"/>
+        <v>3.0878999999999999</v>
+      </c>
+      <c r="Q19" s="42">
+        <f>R19*M19</f>
+        <v>223.245</v>
+      </c>
+      <c r="R19" s="28">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="S19" s="29">
+        <f t="shared" si="1"/>
+        <v>223.245</v>
+      </c>
+      <c r="T19" s="56"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
     </row>
@@ -2659,40 +3153,54 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="116"/>
+      <c r="C20" s="101" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="60" t="s">
+      <c r="D20" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="35"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="36"/>
+      <c r="H20" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="K20" s="63" t="s">
+        <v>53</v>
+      </c>
       <c r="L20" s="10">
         <v>20</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="64">
+        <f t="shared" si="2"/>
+        <v>2420</v>
+      </c>
+      <c r="N20" s="80"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="67">
         <f t="shared" si="0"/>
-        <v>2420</v>
-      </c>
-      <c r="N20" s="37"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="68"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
     </row>
@@ -2700,42 +3208,65 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="36"/>
+      <c r="H21" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="I21" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K21" s="51">
+        <v>120</v>
+      </c>
       <c r="L21" s="2">
         <v>1</v>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="51">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N21" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21" s="53">
+        <v>2.46E-2</v>
+      </c>
+      <c r="P21" s="72">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N21" s="37"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="36"/>
+        <v>2.46E-2</v>
+      </c>
+      <c r="Q21" s="54">
+        <f>R21*K21</f>
+        <v>2.952</v>
+      </c>
+      <c r="R21" s="53">
+        <v>2.46E-2</v>
+      </c>
+      <c r="S21" s="72">
+        <f t="shared" si="1"/>
+        <v>2.9766000000000004</v>
+      </c>
+      <c r="T21" s="55"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
     </row>
@@ -2743,8 +3274,8 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="59" t="s">
+      <c r="B22" s="115"/>
+      <c r="C22" s="103" t="s">
         <v>132</v>
       </c>
       <c r="D22" s="8" t="s">
@@ -2759,24 +3290,47 @@
       <c r="G22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="64">
+      <c r="H22" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K22" s="26">
+        <v>121</v>
+      </c>
+      <c r="L22" s="39">
         <v>1</v>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N22" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="28">
+        <v>0.2545</v>
+      </c>
+      <c r="P22" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="36"/>
+        <v>0.2545</v>
+      </c>
+      <c r="Q22" s="42">
+        <f>R22*K22</f>
+        <v>20.654699999999998</v>
+      </c>
+      <c r="R22" s="28">
+        <v>0.17069999999999999</v>
+      </c>
+      <c r="S22" s="29">
+        <f t="shared" si="1"/>
+        <v>20.654700000000002</v>
+      </c>
+      <c r="T22" s="56"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
     </row>
@@ -2784,40 +3338,49 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="34" t="s">
+      <c r="B23" s="116"/>
+      <c r="C23" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="H23" s="35"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="36"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="64"/>
       <c r="L23" s="10">
         <v>1</v>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="64">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N23" s="82"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="67">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N23" s="42"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="77">
+        <f t="shared" ref="Q23:Q24" si="3">R23*K23</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="66"/>
+      <c r="S23" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="68"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
     </row>
@@ -2825,42 +3388,65 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="83" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="H24" s="35"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="65">
+      <c r="H24" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="85" t="s">
+        <v>252</v>
+      </c>
+      <c r="K24" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="86">
         <v>1</v>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="87">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N24" s="88" t="s">
+        <v>240</v>
+      </c>
+      <c r="O24" s="89">
+        <v>0.12231</v>
+      </c>
+      <c r="P24" s="90">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="36"/>
+        <v>0.12231</v>
+      </c>
+      <c r="Q24" s="91">
+        <f>R24*M24</f>
+        <v>9.6739499999999996</v>
+      </c>
+      <c r="R24" s="89">
+        <v>7.9949999999999993E-2</v>
+      </c>
+      <c r="S24" s="90">
+        <f t="shared" si="1"/>
+        <v>9.6739499999999996</v>
+      </c>
+      <c r="T24" s="122"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
     </row>
@@ -2868,42 +3454,65 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="114" t="s">
         <v>223</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="11">
+      <c r="H25" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="I25" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K25" s="47">
+        <v>121</v>
+      </c>
+      <c r="L25" s="2">
         <v>1</v>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="51">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N25" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="O25" s="53">
+        <v>0.25850000000000001</v>
+      </c>
+      <c r="P25" s="72">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N25" s="42"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="38"/>
-      <c r="S25" s="39"/>
-      <c r="T25" s="36"/>
+        <v>0.25850000000000001</v>
+      </c>
+      <c r="Q25" s="54">
+        <f>R25*M25</f>
+        <v>21.247600000000002</v>
+      </c>
+      <c r="R25" s="53">
+        <v>0.17560000000000001</v>
+      </c>
+      <c r="S25" s="72">
+        <f t="shared" si="1"/>
+        <v>21.247600000000002</v>
+      </c>
+      <c r="T25" s="55"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
     </row>
@@ -2911,40 +3520,63 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="34" t="s">
+      <c r="B26" s="116"/>
+      <c r="C26" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="35"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="66">
+      <c r="H26" s="75" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="K26" s="60">
+        <v>121</v>
+      </c>
+      <c r="L26" s="10">
         <v>1</v>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="64">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N26" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="O26" s="66">
+        <v>0.47610000000000002</v>
+      </c>
+      <c r="P26" s="67">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N26" s="42"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="38"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="36"/>
+        <v>0.47610000000000002</v>
+      </c>
+      <c r="Q26" s="77">
+        <f>R26*K26</f>
+        <v>39.058799999999998</v>
+      </c>
+      <c r="R26" s="66">
+        <v>0.32279999999999998</v>
+      </c>
+      <c r="S26" s="67">
+        <f t="shared" si="1"/>
+        <v>39.058800000000005</v>
+      </c>
+      <c r="T26" s="68"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
     </row>
@@ -2952,44 +3584,65 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="60" t="s">
+      <c r="D27" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="35"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8" t="s">
+      <c r="H27" s="81" t="s">
+        <v>259</v>
+      </c>
+      <c r="I27" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="K27" s="8"/>
+      <c r="K27" s="47">
+        <v>5600</v>
+      </c>
       <c r="L27" s="2">
         <v>46</v>
       </c>
-      <c r="M27" s="36">
+      <c r="M27" s="51">
+        <f t="shared" si="2"/>
+        <v>5566</v>
+      </c>
+      <c r="N27" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="O27" s="53">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="P27" s="72">
         <f t="shared" si="0"/>
-        <v>5566</v>
-      </c>
-      <c r="N27" s="42"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="39"/>
-      <c r="T27" s="36"/>
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="Q27" s="54">
+        <f>R27*M27</f>
+        <v>3.8961999999999999</v>
+      </c>
+      <c r="R27" s="53">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S27" s="72">
+        <f t="shared" si="1"/>
+        <v>3.8961999999999999</v>
+      </c>
+      <c r="T27" s="55"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
     </row>
@@ -2997,8 +3650,8 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="34" t="s">
+      <c r="B28" s="115"/>
+      <c r="C28" s="108" t="s">
         <v>154</v>
       </c>
       <c r="D28" s="8" t="s">
@@ -3013,26 +3666,47 @@
       <c r="G28" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="35"/>
-      <c r="I28" s="8"/>
+      <c r="H28" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J28" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="K28" s="8"/>
+      <c r="K28" s="8">
+        <v>200</v>
+      </c>
       <c r="L28" s="6">
         <v>1</v>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N28" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O28" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="P28" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N28" s="42"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="36"/>
+        <v>1E-3</v>
+      </c>
+      <c r="Q28" s="42">
+        <f>R28*K28</f>
+        <v>0.2</v>
+      </c>
+      <c r="R28" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="S28" s="29">
+        <f t="shared" si="1"/>
+        <v>0.12100000000000001</v>
+      </c>
+      <c r="T28" s="56"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
     </row>
@@ -3040,8 +3714,8 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="34" t="s">
+      <c r="B29" s="115"/>
+      <c r="C29" s="108" t="s">
         <v>157</v>
       </c>
       <c r="D29" s="8" t="s">
@@ -3056,26 +3730,47 @@
       <c r="G29" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="35"/>
-      <c r="I29" s="8"/>
+      <c r="H29" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J29" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="K29" s="8"/>
+      <c r="K29" s="8">
+        <v>600</v>
+      </c>
       <c r="L29" s="6">
         <v>5</v>
       </c>
-      <c r="M29" s="36">
+      <c r="M29" s="26">
+        <f t="shared" si="2"/>
+        <v>605</v>
+      </c>
+      <c r="N29" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29" s="28">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P29" s="29">
         <f t="shared" si="0"/>
-        <v>605</v>
-      </c>
-      <c r="N29" s="42"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="39"/>
-      <c r="T29" s="36"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="Q29" s="42">
+        <f>R29*K29</f>
+        <v>0.9</v>
+      </c>
+      <c r="R29" s="28">
+        <v>1.5E-3</v>
+      </c>
+      <c r="S29" s="29">
+        <f t="shared" si="1"/>
+        <v>0.90749999999999997</v>
+      </c>
+      <c r="T29" s="56"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
     </row>
@@ -3083,8 +3778,8 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="34" t="s">
+      <c r="B30" s="115"/>
+      <c r="C30" s="108" t="s">
         <v>160</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -3099,26 +3794,47 @@
       <c r="G30" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
+      <c r="H30" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J30" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K30" s="8"/>
+      <c r="K30" s="8">
+        <v>200</v>
+      </c>
       <c r="L30" s="6">
         <v>1</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N30" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30" s="28">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P30" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N30" s="42"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="39"/>
-      <c r="T30" s="36"/>
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="42">
+        <f>R30*K30</f>
+        <v>0.24</v>
+      </c>
+      <c r="R30" s="28">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="S30" s="29">
+        <f t="shared" si="1"/>
+        <v>0.1452</v>
+      </c>
+      <c r="T30" s="56"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
     </row>
@@ -3126,8 +3842,8 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="34" t="s">
+      <c r="B31" s="115"/>
+      <c r="C31" s="108" t="s">
         <v>162</v>
       </c>
       <c r="D31" s="8" t="s">
@@ -3142,26 +3858,47 @@
       <c r="G31" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
+      <c r="H31" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J31" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="K31" s="36"/>
+      <c r="K31" s="26">
+        <v>300</v>
+      </c>
       <c r="L31" s="6">
         <v>2</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N31" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="P31" s="29">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N31" s="37"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="36"/>
+        <v>2E-3</v>
+      </c>
+      <c r="Q31" s="42">
+        <f>R31*K31</f>
+        <v>0.3</v>
+      </c>
+      <c r="R31" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="S31" s="29">
+        <f t="shared" si="1"/>
+        <v>0.24200000000000002</v>
+      </c>
+      <c r="T31" s="56"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
     </row>
@@ -3169,8 +3906,8 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="34" t="s">
+      <c r="B32" s="115"/>
+      <c r="C32" s="108" t="s">
         <v>165</v>
       </c>
       <c r="D32" s="8" t="s">
@@ -3185,26 +3922,47 @@
       <c r="G32" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H32" s="35"/>
-      <c r="I32" s="41"/>
+      <c r="H32" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J32" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="K32" s="36"/>
+      <c r="K32" s="26">
+        <v>200</v>
+      </c>
       <c r="L32" s="6">
         <v>1</v>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N32" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O32" s="28">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P32" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N32" s="37"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="39"/>
-      <c r="Q32" s="39"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="39"/>
-      <c r="T32" s="36"/>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q32" s="42">
+        <f>R32*K32</f>
+        <v>0.22</v>
+      </c>
+      <c r="R32" s="28">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="S32" s="29">
+        <f t="shared" si="1"/>
+        <v>0.13310000000000002</v>
+      </c>
+      <c r="T32" s="56"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
     </row>
@@ -3212,8 +3970,8 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="34" t="s">
+      <c r="B33" s="115"/>
+      <c r="C33" s="108" t="s">
         <v>167</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -3228,26 +3986,47 @@
       <c r="G33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H33" s="35"/>
-      <c r="I33" s="43"/>
+      <c r="H33" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J33" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="K33" s="36"/>
+      <c r="K33" s="26">
+        <v>200</v>
+      </c>
       <c r="L33" s="6">
         <v>1</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N33" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O33" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="P33" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N33" s="37"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="39"/>
-      <c r="T33" s="36"/>
+        <v>1E-3</v>
+      </c>
+      <c r="Q33" s="42">
+        <f>R33*K33</f>
+        <v>0.2</v>
+      </c>
+      <c r="R33" s="28">
+        <v>1E-3</v>
+      </c>
+      <c r="S33" s="29">
+        <f t="shared" si="1"/>
+        <v>0.12100000000000001</v>
+      </c>
+      <c r="T33" s="56"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
     </row>
@@ -3255,8 +4034,8 @@
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="34" t="s">
+      <c r="B34" s="115"/>
+      <c r="C34" s="108" t="s">
         <v>170</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -3271,26 +4050,47 @@
       <c r="G34" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="8"/>
+      <c r="H34" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>273</v>
+      </c>
       <c r="J34" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="K34" s="36"/>
+      <c r="K34" s="26">
+        <v>600</v>
+      </c>
       <c r="L34" s="6">
         <v>5</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="26">
+        <f t="shared" si="2"/>
+        <v>605</v>
+      </c>
+      <c r="N34" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O34" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P34" s="29">
         <f t="shared" si="0"/>
-        <v>605</v>
-      </c>
-      <c r="N34" s="37"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="39"/>
-      <c r="T34" s="36"/>
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="Q34" s="42">
+        <f t="shared" ref="Q34:Q38" si="4">R34*K34</f>
+        <v>0.42</v>
+      </c>
+      <c r="R34" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S34" s="29">
+        <f t="shared" si="1"/>
+        <v>0.42349999999999999</v>
+      </c>
+      <c r="T34" s="56"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
     </row>
@@ -3298,8 +4098,8 @@
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="34" t="s">
+      <c r="B35" s="115"/>
+      <c r="C35" s="108" t="s">
         <v>174</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -3314,26 +4114,47 @@
       <c r="G35" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="8"/>
+      <c r="H35" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J35" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K35" s="36"/>
+      <c r="K35" s="26">
+        <v>800</v>
+      </c>
       <c r="L35" s="6">
         <v>6</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="26">
+        <f t="shared" si="2"/>
+        <v>726.00000000000011</v>
+      </c>
+      <c r="N35" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="O35" s="28">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="P35" s="29">
         <f t="shared" si="0"/>
-        <v>726.00000000000011</v>
-      </c>
-      <c r="N35" s="37"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="39"/>
-      <c r="T35" s="36"/>
+        <v>1.8000000000000002E-2</v>
+      </c>
+      <c r="Q35" s="42">
+        <f t="shared" si="4"/>
+        <v>2.4</v>
+      </c>
+      <c r="R35" s="28">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="S35" s="29">
+        <f t="shared" si="1"/>
+        <v>2.1780000000000004</v>
+      </c>
+      <c r="T35" s="56"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
     </row>
@@ -3341,8 +4162,8 @@
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="28" t="s">
+      <c r="B36" s="115"/>
+      <c r="C36" s="99" t="s">
         <v>178</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -3357,26 +4178,47 @@
       <c r="G36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="8"/>
+      <c r="H36" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>275</v>
+      </c>
       <c r="J36" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="K36" s="36"/>
+      <c r="K36" s="26">
+        <v>250</v>
+      </c>
       <c r="L36" s="6">
         <v>2</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="26">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N36" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O36" s="37">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="P36" s="29">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N36" s="61"/>
-      <c r="O36" s="62"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="62"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="54"/>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q36" s="42">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="R36" s="37">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="S36" s="29">
+        <f t="shared" si="1"/>
+        <v>0.38720000000000004</v>
+      </c>
+      <c r="T36" s="58"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
     </row>
@@ -3384,8 +4226,8 @@
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="49"/>
-      <c r="C37" s="28" t="s">
+      <c r="B37" s="115"/>
+      <c r="C37" s="99" t="s">
         <v>180</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -3400,26 +4242,47 @@
       <c r="G37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="8"/>
+      <c r="H37" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J37" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="K37" s="36"/>
+      <c r="K37" s="26">
+        <v>500</v>
+      </c>
       <c r="L37" s="6">
         <v>4</v>
       </c>
-      <c r="M37" s="36">
+      <c r="M37" s="26">
+        <f t="shared" si="2"/>
+        <v>484.00000000000006</v>
+      </c>
+      <c r="N37" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O37" s="28">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P37" s="29">
         <f t="shared" si="0"/>
-        <v>484.00000000000006</v>
-      </c>
-      <c r="N37" s="42"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="39"/>
-      <c r="Q37" s="39"/>
-      <c r="R37" s="38"/>
-      <c r="S37" s="39"/>
-      <c r="T37" s="36"/>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="Q37" s="42">
+        <f t="shared" si="4"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R37" s="28">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="S37" s="29">
+        <f t="shared" si="1"/>
+        <v>0.5324000000000001</v>
+      </c>
+      <c r="T37" s="56"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
     </row>
@@ -3427,11 +4290,11 @@
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="55" t="s">
+      <c r="B38" s="115"/>
+      <c r="C38" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="35" t="s">
         <v>184</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -3443,26 +4306,47 @@
       <c r="G38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="8"/>
+      <c r="H38" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J38" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="K38" s="36"/>
+      <c r="K38" s="26">
+        <v>2500</v>
+      </c>
       <c r="L38" s="6">
         <v>20</v>
       </c>
-      <c r="M38" s="36">
+      <c r="M38" s="26">
+        <f t="shared" si="2"/>
+        <v>2420</v>
+      </c>
+      <c r="N38" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O38" s="28">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P38" s="29">
         <f t="shared" si="0"/>
-        <v>2420</v>
-      </c>
-      <c r="N38" s="42"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="39"/>
-      <c r="T38" s="36"/>
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="Q38" s="42">
+        <f>R38*K38</f>
+        <v>2.25</v>
+      </c>
+      <c r="R38" s="28">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="S38" s="29">
+        <f t="shared" si="1"/>
+        <v>2.1779999999999999</v>
+      </c>
+      <c r="T38" s="56"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
     </row>
@@ -3470,8 +4354,8 @@
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="28" t="s">
+      <c r="B39" s="115"/>
+      <c r="C39" s="99" t="s">
         <v>186</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -3486,26 +4370,47 @@
       <c r="G39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="8"/>
+      <c r="H39" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J39" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="K39" s="36"/>
+      <c r="K39" s="26">
+        <v>200</v>
+      </c>
       <c r="L39" s="6">
         <v>1</v>
       </c>
-      <c r="M39" s="36">
+      <c r="M39" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N39" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O39" s="28">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="P39" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N39" s="42"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="54"/>
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Q39" s="42">
+        <f>R39*K39</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R39" s="28">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="S39" s="29">
+        <f t="shared" si="1"/>
+        <v>0.20570000000000002</v>
+      </c>
+      <c r="T39" s="58"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
     </row>
@@ -3513,8 +4418,8 @@
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="28" t="s">
+      <c r="B40" s="115"/>
+      <c r="C40" s="99" t="s">
         <v>189</v>
       </c>
       <c r="D40" s="8" t="s">
@@ -3529,26 +4434,47 @@
       <c r="G40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="8"/>
+      <c r="H40" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="J40" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="K40" s="36"/>
+      <c r="K40" s="26">
+        <v>500</v>
+      </c>
       <c r="L40" s="6">
         <v>4</v>
       </c>
-      <c r="M40" s="36">
+      <c r="M40" s="26">
+        <f t="shared" si="2"/>
+        <v>484.00000000000006</v>
+      </c>
+      <c r="N40" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" s="28">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="P40" s="29">
         <f t="shared" si="0"/>
-        <v>484.00000000000006</v>
-      </c>
-      <c r="N40" s="42"/>
-      <c r="O40" s="38"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="38"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="54"/>
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="Q40" s="42">
+        <f>R40*K40</f>
+        <v>1.45</v>
+      </c>
+      <c r="R40" s="28">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="S40" s="29">
+        <f t="shared" si="1"/>
+        <v>1.4036</v>
+      </c>
+      <c r="T40" s="58"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
     </row>
@@ -3556,42 +4482,63 @@
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="55" t="s">
+      <c r="B41" s="116"/>
+      <c r="C41" s="109" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="60" t="s">
+      <c r="D41" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8" t="s">
+      <c r="H41" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="I41" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="K41" s="36"/>
-      <c r="L41" s="67">
+      <c r="K41" s="64">
+        <v>2700</v>
+      </c>
+      <c r="L41" s="40">
         <v>22</v>
       </c>
-      <c r="M41" s="36">
+      <c r="M41" s="64">
+        <f t="shared" si="2"/>
+        <v>2662</v>
+      </c>
+      <c r="N41" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="O41" s="66">
+        <v>1.1089999999999999E-2</v>
+      </c>
+      <c r="P41" s="67">
         <f t="shared" si="0"/>
-        <v>2662</v>
-      </c>
-      <c r="N41" s="42"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="38"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="56"/>
+        <v>0.24397999999999997</v>
+      </c>
+      <c r="Q41" s="67">
+        <f>R41*K41</f>
+        <v>29.942999999999998</v>
+      </c>
+      <c r="R41" s="66">
+        <v>1.1089999999999999E-2</v>
+      </c>
+      <c r="S41" s="67">
+        <f t="shared" si="1"/>
+        <v>29.521579999999997</v>
+      </c>
+      <c r="T41" s="92"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
     </row>
@@ -3599,42 +4546,65 @@
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="52" t="s">
+      <c r="B42" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" s="105" t="s">
         <v>195</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="83" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="68">
+      <c r="H42" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="J42" s="85" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="87">
+        <v>120</v>
+      </c>
+      <c r="L42" s="93">
         <v>1</v>
       </c>
-      <c r="M42" s="36">
+      <c r="M42" s="87">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N42" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="89">
+        <v>0.13389999999999999</v>
+      </c>
+      <c r="P42" s="90">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N42" s="42"/>
-      <c r="O42" s="38"/>
-      <c r="P42" s="39"/>
-      <c r="Q42" s="39"/>
-      <c r="R42" s="38"/>
-      <c r="S42" s="39"/>
-      <c r="T42" s="36"/>
+        <v>0.13389999999999999</v>
+      </c>
+      <c r="Q42" s="90">
+        <f>R42*K42</f>
+        <v>12.864000000000001</v>
+      </c>
+      <c r="R42" s="89">
+        <v>0.1072</v>
+      </c>
+      <c r="S42" s="90">
+        <f t="shared" si="1"/>
+        <v>12.971200000000001</v>
+      </c>
+      <c r="T42" s="122"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
     </row>
@@ -3642,42 +4612,65 @@
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" s="106" t="s">
         <v>199</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="47" t="s">
         <v>201</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="11">
+      <c r="H43" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I43" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J43" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K43" s="51">
+        <v>300</v>
+      </c>
+      <c r="L43" s="2">
         <v>2</v>
       </c>
-      <c r="M43" s="36">
+      <c r="M43" s="51">
+        <f t="shared" si="2"/>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="N43" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="O43" s="72">
+        <v>0.49959999999999999</v>
+      </c>
+      <c r="P43" s="72">
         <f t="shared" si="0"/>
-        <v>242.00000000000003</v>
-      </c>
-      <c r="N43" s="8"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="39"/>
-      <c r="R43" s="39"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="56"/>
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="Q43" s="72">
+        <f t="shared" ref="Q43:Q46" si="5">R43*K43</f>
+        <v>94.679999999999993</v>
+      </c>
+      <c r="R43" s="72">
+        <v>0.31559999999999999</v>
+      </c>
+      <c r="S43" s="72">
+        <f t="shared" si="1"/>
+        <v>76.375200000000007</v>
+      </c>
+      <c r="T43" s="79"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
     </row>
@@ -3685,8 +4678,8 @@
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="49"/>
-      <c r="C44" s="34" t="s">
+      <c r="B44" s="115"/>
+      <c r="C44" s="108" t="s">
         <v>202</v>
       </c>
       <c r="D44" s="8" t="s">
@@ -3701,24 +4694,47 @@
       <c r="G44" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="H44" s="35"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="36"/>
+      <c r="H44" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K44" s="26">
+        <v>121</v>
+      </c>
       <c r="L44" s="6">
         <v>1</v>
       </c>
-      <c r="M44" s="36">
+      <c r="M44" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N44" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="28">
+        <v>0.26</v>
+      </c>
+      <c r="P44" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N44" s="42"/>
-      <c r="O44" s="38"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="38"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="36"/>
+        <v>0.26</v>
+      </c>
+      <c r="Q44" s="29">
+        <f t="shared" si="5"/>
+        <v>21.864699999999999</v>
+      </c>
+      <c r="R44" s="28">
+        <v>0.1807</v>
+      </c>
+      <c r="S44" s="29">
+        <f t="shared" si="1"/>
+        <v>21.864700000000003</v>
+      </c>
+      <c r="T44" s="56"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
     </row>
@@ -3726,8 +4742,8 @@
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="34" t="s">
+      <c r="B45" s="115"/>
+      <c r="C45" s="108" t="s">
         <v>205</v>
       </c>
       <c r="D45" s="8" t="s">
@@ -3742,24 +4758,47 @@
       <c r="G45" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="H45" s="35"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="36"/>
+      <c r="H45" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I45" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K45" s="31" t="s">
+        <v>252</v>
+      </c>
       <c r="L45" s="6">
         <v>1</v>
       </c>
-      <c r="M45" s="36">
+      <c r="M45" s="26">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N45" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="O45" s="28">
+        <v>18.032879999999999</v>
+      </c>
+      <c r="P45" s="29">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N45" s="42"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="39"/>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="36"/>
+        <v>18.032879999999999</v>
+      </c>
+      <c r="Q45" s="42">
+        <f>R45*M45</f>
+        <v>1744.3589900000002</v>
+      </c>
+      <c r="R45" s="28">
+        <v>14.41619</v>
+      </c>
+      <c r="S45" s="29">
+        <f t="shared" si="1"/>
+        <v>1744.3589900000002</v>
+      </c>
+      <c r="T45" s="56"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
     </row>
@@ -3767,40 +4806,63 @@
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="34" t="s">
+      <c r="B46" s="116"/>
+      <c r="C46" s="104" t="s">
         <v>208</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="H46" s="43"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="66">
+      <c r="H46" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="J46" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="K46" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="L46" s="10">
         <v>5</v>
       </c>
-      <c r="M46" s="36">
+      <c r="M46" s="64">
+        <f t="shared" si="2"/>
+        <v>605</v>
+      </c>
+      <c r="N46" s="80" t="s">
+        <v>271</v>
+      </c>
+      <c r="O46" s="66">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="P46" s="67">
         <f t="shared" si="0"/>
-        <v>605</v>
-      </c>
-      <c r="N46" s="37"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="39"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="36"/>
+        <v>1.29</v>
+      </c>
+      <c r="Q46" s="77">
+        <f>R46*M46</f>
+        <v>128.86500000000001</v>
+      </c>
+      <c r="R46" s="66">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="S46" s="67">
+        <f t="shared" si="1"/>
+        <v>128.86500000000001</v>
+      </c>
+      <c r="T46" s="68"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
     </row>
@@ -3808,42 +4870,65 @@
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="106" t="s">
         <v>212</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="H47" s="35"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="36"/>
+      <c r="H47" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I47" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J47" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K47" s="69" t="s">
+        <v>252</v>
+      </c>
       <c r="L47" s="2">
         <v>1</v>
       </c>
-      <c r="M47" s="36">
+      <c r="M47" s="51">
+        <f t="shared" si="2"/>
+        <v>121.00000000000001</v>
+      </c>
+      <c r="N47" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="O47" s="53">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="P47" s="72">
         <f t="shared" si="0"/>
-        <v>121.00000000000001</v>
-      </c>
-      <c r="N47" s="37"/>
-      <c r="O47" s="38"/>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="40"/>
-      <c r="S47" s="39"/>
-      <c r="T47" s="36"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="Q47" s="54">
+        <f>R47*M47</f>
+        <v>59.411000000000008</v>
+      </c>
+      <c r="R47" s="94">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="S47" s="72">
+        <f t="shared" si="1"/>
+        <v>59.411000000000008</v>
+      </c>
+      <c r="T47" s="55"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
     </row>
@@ -3851,8 +4936,8 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="34" t="s">
+      <c r="B48" s="115"/>
+      <c r="C48" s="108" t="s">
         <v>214</v>
       </c>
       <c r="D48" s="8" t="s">
@@ -3867,24 +4952,24 @@
       <c r="G48" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="H48" s="43"/>
+      <c r="H48" s="32"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="69">
+      <c r="K48" s="26"/>
+      <c r="L48" s="41">
         <v>1</v>
       </c>
-      <c r="M48" s="36">
-        <f t="shared" si="0"/>
+      <c r="M48" s="26">
+        <f t="shared" si="2"/>
         <v>121.00000000000001</v>
       </c>
-      <c r="N48" s="37"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="39"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="39"/>
-      <c r="T48" s="56"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="59"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
     </row>
@@ -3892,8 +4977,8 @@
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="49"/>
-      <c r="C49" s="34" t="s">
+      <c r="B49" s="115"/>
+      <c r="C49" s="108" t="s">
         <v>217</v>
       </c>
       <c r="D49" s="8" t="s">
@@ -3915,125 +5000,126 @@
       <c r="L49" s="6">
         <v>2</v>
       </c>
-      <c r="M49" s="36">
-        <f t="shared" si="0"/>
+      <c r="M49" s="26">
+        <f t="shared" si="2"/>
         <v>242.00000000000003</v>
       </c>
-      <c r="N49" s="37"/>
-      <c r="O49" s="38"/>
-      <c r="P49" s="39"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="38"/>
-      <c r="S49" s="39"/>
-      <c r="T49" s="36"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="56"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50" s="123">
         <v>48</v>
       </c>
-      <c r="B50" s="50"/>
-      <c r="C50" s="34" t="s">
+      <c r="B50" s="116"/>
+      <c r="C50" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="60" t="s">
+      <c r="G50" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="29">
+      <c r="H50" s="95" t="s">
+        <v>53</v>
+      </c>
+      <c r="I50" s="95" t="s">
+        <v>53</v>
+      </c>
+      <c r="J50" s="96" t="s">
+        <v>252</v>
+      </c>
+      <c r="K50" s="95" t="s">
+        <v>252</v>
+      </c>
+      <c r="L50" s="24">
         <v>7</v>
       </c>
-      <c r="M50" s="36">
-        <f t="shared" si="0"/>
+      <c r="M50" s="64">
+        <f t="shared" si="2"/>
         <v>847.00000000000011</v>
       </c>
-      <c r="N50" s="37"/>
-      <c r="O50" s="38"/>
-      <c r="P50" s="39"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="38"/>
-      <c r="S50" s="39"/>
-      <c r="T50" s="36"/>
+      <c r="N50" s="97"/>
+      <c r="O50" s="66"/>
+      <c r="P50" s="67"/>
+      <c r="Q50" s="67"/>
+      <c r="R50" s="66"/>
+      <c r="S50" s="67"/>
+      <c r="T50" s="68"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="33" t="s">
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="M51" s="33"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="33"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="21">
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17">
         <f>SUM(Q3:Q50)</f>
-        <v>261.30090000000001</v>
-      </c>
-      <c r="R51" s="21"/>
-      <c r="S51" s="13">
+        <v>2766.0265799999997</v>
+      </c>
+      <c r="R51" s="17"/>
+      <c r="S51" s="12">
         <f>SUM(S3:S50)</f>
-        <v>260.18630000000007</v>
-      </c>
-      <c r="T51" s="17"/>
+        <v>2745.1463600000006</v>
+      </c>
+      <c r="T51" s="14"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="30" t="s">
+      <c r="H52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="13">
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
+      <c r="O52" s="45"/>
+      <c r="P52" s="12">
         <f>SUM(P3:P50)</f>
-        <v>3.8005200000000006</v>
-      </c>
-      <c r="Q52" s="13"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="20">
+        <v>30.454219999999999</v>
+      </c>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="16">
         <f>S51/5</f>
-        <v>52.037260000000018</v>
-      </c>
-      <c r="T52" s="17"/>
+        <v>549.02927200000011</v>
+      </c>
+      <c r="T52" s="14"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="J54" s="14"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
     </row>
@@ -4278,9 +5364,43 @@
     <hyperlink ref="N9" r:id="rId7"/>
     <hyperlink ref="N10" r:id="rId8"/>
     <hyperlink ref="N11" r:id="rId9"/>
+    <hyperlink ref="N12" r:id="rId10"/>
+    <hyperlink ref="N13" r:id="rId11"/>
+    <hyperlink ref="N14" r:id="rId12"/>
+    <hyperlink ref="N15" r:id="rId13"/>
+    <hyperlink ref="N16" r:id="rId14"/>
+    <hyperlink ref="N17" r:id="rId15"/>
+    <hyperlink ref="N18" r:id="rId16"/>
+    <hyperlink ref="N19" r:id="rId17"/>
+    <hyperlink ref="N21" r:id="rId18"/>
+    <hyperlink ref="N22" r:id="rId19"/>
+    <hyperlink ref="N24" r:id="rId20"/>
+    <hyperlink ref="N25" r:id="rId21"/>
+    <hyperlink ref="N26" r:id="rId22"/>
+    <hyperlink ref="N27" r:id="rId23"/>
+    <hyperlink ref="N28" r:id="rId24"/>
+    <hyperlink ref="N29" r:id="rId25"/>
+    <hyperlink ref="N30" r:id="rId26"/>
+    <hyperlink ref="N31" r:id="rId27"/>
+    <hyperlink ref="N32" r:id="rId28"/>
+    <hyperlink ref="N33" r:id="rId29"/>
+    <hyperlink ref="N35" r:id="rId30"/>
+    <hyperlink ref="N37" r:id="rId31"/>
+    <hyperlink ref="N38" r:id="rId32"/>
+    <hyperlink ref="N39" r:id="rId33"/>
+    <hyperlink ref="N40" r:id="rId34"/>
+    <hyperlink ref="N41" r:id="rId35"/>
+    <hyperlink ref="N42" r:id="rId36"/>
+    <hyperlink ref="N43" r:id="rId37"/>
+    <hyperlink ref="N44" r:id="rId38"/>
+    <hyperlink ref="N45" r:id="rId39"/>
+    <hyperlink ref="N46" r:id="rId40"/>
+    <hyperlink ref="N47" r:id="rId41"/>
+    <hyperlink ref="N34" r:id="rId42"/>
+    <hyperlink ref="N36" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId44"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
